--- a/config/auto_configs/2020_Hyundai_Hyundai_Nexo(FE)_113kW.xlsx
+++ b/config/auto_configs/2020_Hyundai_Hyundai_Nexo(FE)_113kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +855,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HMA_0041B</t>
+          <t>HMA_0042C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HMA_0041B</t>
+          <t>HMA_0042C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HMA_0041B</t>
+          <t>HMA_0042C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HMA_0041B</t>
+          <t>HMA_0042C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HMA_0042C</t>
+          <t>HMA_0041B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HMA_0042C</t>
+          <t>HMA_0041B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HMA_0042C</t>
+          <t>HMA_0041B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HMA_0042C</t>
+          <t>HMA_0041B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1018,6 +1018,776 @@
         </is>
       </c>
       <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_003C9</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_00377</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AFC-D</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_0041A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AFC-P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_0041E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AFC-RL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_00416</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AFC-RR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_00427</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_003C1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_HK_00063</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_10693</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BCW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HMA_00424</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BHDC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HMA_00419</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HMA_00422</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BPCU</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HMA_00425</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMA_002B0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HMA_003C4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HMA_0037E</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FCA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HMA_00423</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FCU</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HMA_00428</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HMA_00418</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HMU</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HMA_0042A</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HMA_003BF</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HMA_003C3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HMA_0041C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LDC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HMA_0041F</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HMA_00417</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HMA_0026A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HMA_003CF</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RF-L</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HMA_00420</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RF-R</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HMA_0041D</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RSPA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HMA_00421</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HMA_003FC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HMA_0042B</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SVMS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HMA_003F2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HMA_0030E</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HMA_0032F</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>00</t>
         </is>
